--- a/data/credit_bond_2026-08-03.xlsx
+++ b/data/credit_bond_2026-08-03.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-03" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-04" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -37,6 +37,10 @@
       <sz val="12.0"/>
       <color indexed="8"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="12.0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -90,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
@@ -99,6 +103,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -149,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY1"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -163,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
     </row>
@@ -668,6 +678,235 @@
           <t>团费(%)</t>
         </is>
       </c>
+    </row>
+    <row r="3" customHeight="true" ht="18.0">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>26农业银行绿色债01</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>08-03 18:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2628001.IB</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>25农业银行绿色债02</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>3.57Y</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>1.5338</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>中国农业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>08-03 09:00</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>1.52%~1.62%</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,华泰证券股份有限公司,招商证券股份有限公司,中银国际证券股份有限公司,国投证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>中国农业银行股份有限公司2026年绿色金融债券(第一期)(债券通)</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>2029-08-05</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>国有银行</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AY3" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-08-03.xlsx
+++ b/data/credit_bond_2026-08-03.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-04" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-05" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-04</t>
+          <t>数据来源：DM    2026-08-05</t>
         </is>
       </c>
     </row>
@@ -682,87 +682,81 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26农业银行绿色债01</t>
+          <t>26浙商银行永续债</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>08-03 18:00</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>2628001.IB</t>
-        </is>
-      </c>
+          <t>08-05 18:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>100.0</v>
-      </c>
+        <v>300.0</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.80</t>
+          <t>1.65 ~ 2.25</t>
         </is>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25农业银行绿色债02</t>
+          <t>21浙商银行永续债</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>3.57Y</t>
+          <t>113D+N</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.5338</t>
+          <t>1.4867</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4700/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>08-03 09:00</t>
+          <t>08-05 09:00</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
@@ -772,7 +766,7 @@
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.62%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
@@ -787,28 +781,28 @@
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
+          <t>本期债券募集资金将依据适用法律和主管部门的批准用于补充发行人其他一级资本。</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,华泰证券股份有限公司,招商证券股份有限公司,中银国际证券股份有限公司,国投证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,国泰海通证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,中国民生银行股份有限公司,平安银行股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司,北京银行股份有限公司,江苏银行股份有限公司,中银国际证券股份有限公司,中信建投证券股份有限公司,中国银河证券股份有限公司,国投证券股份有限公司,申万宏源证券有限公司,中国国际金融股份有限公司,光大证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>商业银行次级债券</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -818,7 +812,7 @@
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司2026年绿色金融债券(第一期)(债券通)</t>
+          <t>浙商银行股份有限公司2026年无固定期限资本债券(第一期)(债券通)</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
@@ -828,14 +822,10 @@
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>2029-08-05</t>
-        </is>
-      </c>
-      <c r="AJ3" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-07</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3"/>
       <c r="AK3" s="3" t="inlineStr">
         <is>
           <t/>
@@ -843,67 +833,67 @@
       </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>其他一级资本工具</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>国有银行</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AY3" s="3"/>

--- a/data/credit_bond_2026-08-03.xlsx
+++ b/data/credit_bond_2026-08-03.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.4700/--</t>
+          <t>1.4750/1.4700</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">

--- a/data/credit_bond_2026-08-03.xlsx
+++ b/data/credit_bond_2026-08-03.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-05" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-06" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-05</t>
+          <t>数据来源：DM    2026-08-06</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.4750/1.4700</t>
+          <t>1.4800/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -897,6 +897,848 @@
         </is>
       </c>
       <c r="AY3" s="3"/>
+    </row>
+    <row r="4" customHeight="true" ht="18.0">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>26中信银行绿债01BC</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>08-06 18:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>222680012.IB</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>25中信银行绿债01BC</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>1.73Y</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>1.4759</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>08-06 09:00</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>1.53%~1.63%</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025 年版）》规定的绿色产业项目。</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,中国银河证券股份有限公司,中国国际金融股份有限公司,华泰证券股份有限公司,申万宏源证券有限公司,国泰海通证券股份有限公司,国投证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>中信银行股份有限公司2026年绿色金融债券(第一期)(债券通)</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2029-08-10</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AY4" s="3"/>
+    </row>
+    <row r="5" customHeight="true" ht="18.0">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>26西安高新MTN008A</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>08-06 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1.75 ~ 2.75</t>
+        </is>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>西安高新控股有限公司</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>08-06 09:00</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>陕西省-西安市</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>发行人本期中期票据基础发行金额人民币0亿元,发行金额上限人民币10亿元,募集资金全部拟用于偿还发行人到期债务[25西安高新CP009,25西安高新CP010]</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>中国邮政储蓄银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>西安高新控股有限公司2026年度第八期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2029-08-07</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3"/>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AY5" s="3"/>
+    </row>
+    <row r="6" customHeight="true" ht="18.0">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>26华发集团SCP006</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>08-06 18:00</t>
+        </is>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>0.73Y</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>2.06 ~ 2.36</t>
+        </is>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>22华发集团MTN007</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>265D</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2.3589</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>珠海华发集团有限公司</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>08-06 09:00</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>广东省-珠海市</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>本期超短期融资券发行规模为10亿元,用于偿还发行人本部债务融资工具本金。[26华发集团SCP001,21华发集团MTN009]</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>上海银行股份有限公司,北京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>超短期融资券(SCP)</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>珠海华发集团有限公司2026年度第六期超短期融资券</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-30</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AY6" s="3"/>
+    </row>
+    <row r="7" customHeight="true" ht="18.0">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>26西安高新MTN008B</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>08-06 18:00</t>
+        </is>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>西安高新控股有限公司</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>08-06 09:00</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>陕西省-西安市</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>发行人本期中期票据基础发行金额人民币0亿元,发行金额上限人民币10亿元,募集资金全部拟用于偿还发行人到期债务[25西安高新CP009,25西安高新CP010]</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>中国邮政储蓄银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>西安高新控股有限公司2026年度第八期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>2031-08-07</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AY7" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-08-03.xlsx
+++ b/data/credit_bond_2026-08-03.xlsx
@@ -682,7 +682,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26浙商银行永续债</t>
+          <t>26浙商银行永续债01BC</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -690,7 +690,11 @@
           <t>08-05 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>242680031.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>5+N</t>
@@ -699,14 +703,20 @@
       <c r="E3" s="4" t="n">
         <v>300.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>300.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.65 ~ 2.25</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>53.77</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.68</t>
@@ -954,7 +964,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/1.4600</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1134,7 +1144,11 @@
           <t>08-06 18:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>102682951.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -1200,7 +1214,11 @@
           <t>*</t>
         </is>
       </c>
-      <c r="W5" s="3"/>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>2.30%~2.40%</t>
+        </is>
+      </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1337,7 +1355,11 @@
           <t>08-06 18:00</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>012681978.IB</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>0.73Y</t>
@@ -1411,7 +1433,11 @@
           <t>*</t>
         </is>
       </c>
-      <c r="W6" s="3"/>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>2.28%~2.32%</t>
+        </is>
+      </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1548,7 +1574,11 @@
           <t>08-06 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>102682952.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -1614,7 +1644,11 @@
           <t>*</t>
         </is>
       </c>
-      <c r="W7" s="3"/>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>2.49%~2.59%</t>
+        </is>
+      </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
           <t>AAA</t>

--- a/data/credit_bond_2026-08-03.xlsx
+++ b/data/credit_bond_2026-08-03.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-06" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-07" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-06</t>
+          <t>数据来源：DM    2026-08-07</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.4900/1.4600</t>
+          <t>--/1.4600</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1342,7 +1342,9 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AY5" s="3"/>
+      <c r="AY5" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
@@ -1561,7 +1563,9 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AY6" s="3"/>
+      <c r="AY6" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
@@ -1772,7 +1776,220 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="AY7" s="3"/>
+      <c r="AY7" s="4" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="8" customHeight="true" ht="18.0">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>26国耀融汇CP001</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>08-07 18:00</t>
+        </is>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>0.93Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 1.67</t>
+        </is>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>24控租01</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>364D</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>1.7747</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>国耀融汇融资租赁有限公司</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>08-07 09:00</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>发行人本次发行4亿元短期融资券用于偿还发行人即将到期的债务融资工具。[24国药租赁MTN006,24国药租赁MTN007]</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>杭州银行股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>短期融资券(CP)</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>国耀融汇融资租赁有限公司2026年度第一期短期融资券</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AY8" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-08-03.xlsx
+++ b/data/credit_bond_2026-08-03.xlsx
@@ -1163,8 +1163,12 @@
           <t>1.75 ~ 2.75</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>126.13</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -1202,8 +1206,12 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
+      <c r="S5" s="4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>1.57</v>
+      </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -1370,14 +1378,20 @@
       <c r="E6" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>2.06 ~ 2.36</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>123.38</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>2.36</t>
@@ -1791,7 +1805,11 @@
           <t>08-07 18:00</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>042680279.IB</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>0.93Y</t>
@@ -1865,7 +1883,11 @@
           <t>*</t>
         </is>
       </c>
-      <c r="W8" s="3"/>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.72%</t>
+        </is>
+      </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
